--- a/tools/store-list-scraper/output/stores_search.xlsx
+++ b/tools/store-list-scraper/output/stores_search.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店舗リスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4052,8 +4052,3536 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>高田馬場店</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000015/</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>高円寺店</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000018/</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>阿佐ヶ谷店</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000068/</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>国際センター(高田馬場)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000350/</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>蕨店</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000409/</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>大宮東口店</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000402/</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>高田馬場店</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10013/takadanobaba/</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>中野店</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10013/nakano/</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>立川北口店</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10013/tachikawakitaguchi/</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>蒲田店</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10014/kamata/</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>池袋西口店</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10011/ikebukuronishiguchi/</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>千葉店</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10012/chiba/</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>船橋店</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10012/funabashi/</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>横浜西口店</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10016/yokohamanishiguchi/</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>登戸店</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-noborito/</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>大宮店</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-omiya/</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>南浦和店</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-minamiurawa/</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>新宿店</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/shinjuku</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>下北沢店</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/shimo-kitazawa</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>中野店</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/nakano</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>大宮西口店</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/omiya-nishiguchi</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>大宮東口店</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/omiya-higashiguchi</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>立川店</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/tachikawa.html</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>新宿曙橋店</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/hongo.html</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>中野店</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/nakano.html</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>中野南口店</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/nakanominamiguchi.html</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>大宮店</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/omiya.html</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>浦和東口店</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/urawahigashiguchi.html</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>千葉店</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/chiba.html</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>千葉中央店</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/chibachuo.html</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>柏店</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/kashiwa.html</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>立川店</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/tachikawa-hc/</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>吉祥寺店</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/kichijoji-hc/</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>立川南口店</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/tachikawa-minamiguchi-hc/</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>新宿店</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/shinjuku-hc/</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>大宮店</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/omiya-hc/</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>千葉店</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/chiba-hc/</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>渋谷道玄坂店</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/13062320/</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>五反田店</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/13047404/</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>横浜西口店</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/14054808/</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>栄店</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/23004202/</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>名古屋駅東口店</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/23004311/</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>博多駅前店</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/40041121/</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>新宿東口店</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/13041106/</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>新宿東南口店</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/13062327/</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>リブマックス</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>上野店</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://www.livemax.net/livemax-store-list/59749/</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>全国(要確認)</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>八王子店</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10013/hachioji/</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>町田店</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10016/machida/</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>川越店</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10011/kawagoe/</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>浅草橋店</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/asakusabashi.html</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>天王寺店</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/tennouji.html</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>上本町店</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/uehonmachi.html</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>藤沢店</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/fujisawa-hc/</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>CLCコーポレーション</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>浦安店</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://clcnetwork.co.jp/shop_urayasu.html</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>東京東/神奈川/千葉(要確認)</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>八王子店</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-hachioji/</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>立川店</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-tachikawa/</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>橋本店</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-hashimoto/</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>川口店</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/kawaguchi</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>川越店</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/kawagoe</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>草加店</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/soka</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>本厚木店</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/hon-atsugi</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>登戸店</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/noborito</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>橋本店</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/hashimoto</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>赤羽店</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10011/akabane/</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>大井町店</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10014/oimachi/</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>上野店</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/13041142/</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>上大岡店</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/kamiooka.html</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>横浜販売センター</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/yokohama-hc.html</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>横浜ハマボールイアス店</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/yokohamahi.html</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>金山店</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/kanayama-hc/</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>名古屋店</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/nagoya-hc/</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>リブマックス</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>川崎店</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.livemax.net/livemax-store-list/59745/</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>全国(要確認)</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O73"/>
+  <autoFilter ref="A1:O145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tools/store-list-scraper/output/stores_search.xlsx
+++ b/tools/store-list-scraper/output/stores_search.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店舗リスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O145"/>
+  <dimension ref="A1:O172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7580,8 +7580,1331 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>リブマックス</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>名古屋新幹線口店</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.livemax.net/livemax-store-list/59705/</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>全国(要確認)</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>五反田店</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000024/</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>目黒店</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000075/</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>中目黒店</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000355/</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>学芸大学店</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-gakugeidaigaku/</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>春日部店</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/kasukabe</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>新越谷店</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/shin-koshigaya</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>戸塚店</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/totsuka</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>大和店</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10016/yamato/</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>FC八尾店</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/50170044/fc-yao/</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>FC店 検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>FC千里中央店</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/50130013/fc-senrichuominami/</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>FC店 検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>池袋駅前公園店</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/13042901/</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>京橋北口店</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/kyoubashikitaguchi.html</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>本町店</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/honmachi.html</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>越谷店</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/koshigaya-hc/</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>松戸店</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/matsudo-hc/</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>五反田店</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/gotanda-hc/</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>蒲田店</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/kamata-hc/</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>北千住店</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/kitasenju-hc/</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>津田沼店</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/tsudanuma-hc/</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>葛西店</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000071/</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>蒲田店</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/kamata</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>高円寺店</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/koenji</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>自由が丘店</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/jiyugaoka</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>高田馬場店</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/takadanobaba.html</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>横浜東口店</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/14053901/</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>リブマックス</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>五反田店</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://www.livemax.net/livemax-store-list/59753/</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>全国(要確認)</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O145"/>
+  <autoFilter ref="A1:O172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tools/store-list-scraper/output/stores_search.xlsx
+++ b/tools/store-list-scraper/output/stores_search.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店舗リスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O172"/>
+  <dimension ref="A1:O180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8903,8 +8903,400 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>ソレイユ高田馬場店</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/soleil-takadanobaba/</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>ソレイユ業態 検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ソレイユ池袋店</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/soleil-ikebukuro/</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>ソレイユ業態 検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>大阪国際センター</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000836/</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>池袋西口店</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/ikebukuronishi.html</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>西葛西販売センター</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/nishikasai-hc.html</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>上大岡店</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/kamiooka-hc/</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>浦和店</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/urawa-hc/</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>川口店</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/kawaguchi-hc/</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O172"/>
+  <autoFilter ref="A1:O180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tools/store-list-scraper/output/stores_search.xlsx
+++ b/tools/store-list-scraper/output/stores_search.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店舗リスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$200</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O180"/>
+  <dimension ref="A1:O200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9295,8 +9295,988 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>春日部店</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/kasukabe-hc/</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>草加店</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/soka-hc/</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>ハウスコムコミュニケーションズ船橋営業所</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/hcc-funabashi-hc/</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>錦糸町店</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/13064901/</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>練馬店</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-nerima/</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>駒込店</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-komagome/</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>石神井公園店</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-shakujiikoen/</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ひばりヶ丘店</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-hibarigaoka/</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>グランデ新宿店</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/grande-shinjuku/</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>グランデ業態 検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>西船橋店</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/nishi-funabashi</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>本八幡店</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/moto-yawata</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>市川店</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/ichikawa</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>リブマックス</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>関内駅前店</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://www.livemax.net/livemax-store-list/59664/</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>全国(要確認)</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>江坂店</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/esaka.html</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>大阪駅前第3ビル店</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/osakaekimaedai3biru.html</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>大正店</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/taisho.html</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>JR新大阪東口店</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/jrshinosakahigashiguchi.html</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>関内店</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10016/kannai/</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>上大岡店</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10016/kamiooka/</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>名古屋店</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10010/nagoya/</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O180"/>
+  <autoFilter ref="A1:O200"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tools/store-list-scraper/output/stores_search.xlsx
+++ b/tools/store-list-scraper/output/stores_search.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店舗リスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$223</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O200"/>
+  <dimension ref="A1:O223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10275,8 +10275,1135 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>浦和店</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10011/urawa/</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>所沢店</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10011/tokorozawa/</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>大宮西口店</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10011/omiyanishiguchi/</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CLCコーポレーション</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>浅草店</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://clcnetwork.co.jp/shop_asakusa.html</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>東京東/神奈川/千葉(要確認)</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CLCコーポレーション</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>綾瀬店</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://clcnetwork.co.jp/shop_ayase.html</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>東京東/神奈川/千葉(要確認)</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CLCコーポレーション</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>池袋店</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://clcnetwork.co.jp/shop_ikebukuro.html</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>東京東/神奈川/千葉(要確認)</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CLCコーポレーション</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>西葛西店</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://clcnetwork.co.jp/shop_nishikasai.html</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>東京東/神奈川/千葉(要確認)</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CLCコーポレーション</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>川崎店</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://clcnetwork.co.jp/shop_kawasaki.html</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>東京東/神奈川/千葉(要確認)</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CLCコーポレーション</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>横浜店</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://clcnetwork.co.jp/shop_yokohama.html</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>東京東/神奈川/千葉(要確認)</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CLCコーポレーション</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>西船橋店</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://clcnetwork.co.jp/shop_nishifuna.html</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>東京東/神奈川/千葉(要確認)</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>栄店</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000202/</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>金山店</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000212/</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>名古屋駅本店</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000233/</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>名古屋国際センター</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000244/</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>広小路伏見店</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000239/</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>浦和西口店</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/11002436/</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>東大宮店</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/11002406/</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>千葉中央店</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/12041196/</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>上野昭和通り店</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/uenoshowadori.html</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>門前仲町店</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/monzennakacho.html</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>錦糸町店</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/kinshichominamiguchi.html</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>武蔵小杉店</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/musashi-kosugi</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>タウンハウジング</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>恵比寿店</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/store/ebisu</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>直営139店舗(東京/神奈川/埼玉/千葉)</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>https://www.townhousing.co.jp/</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>https://town-group.co.jp/recruit/companies/townhousing</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O200"/>
+  <autoFilter ref="A1:O223"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tools/store-list-scraper/output/stores_search.xlsx
+++ b/tools/store-list-scraper/output/stores_search.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店舗リスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$238</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O223"/>
+  <dimension ref="A1:O238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11402,8 +11402,743 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CLCコーポレーション</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>北千住店</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://clcnetwork.co.jp/shop_senjyu.html</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>東京東/神奈川/千葉(要確認)</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>https://www.clcnet.jp/</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>天神西通り店</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/40049410/</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>西新店</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/40055702/</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>国分寺店</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/13062310/</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>アパマンショップ</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>国分寺北口店</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/shop/13041118/</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>約1,093店舗(2021・賃貸仲介No.1/要確認)</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>https://www.apamanshop.com/</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>https://www.apamannet.com/recruit/</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>船橋北口店</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/funabashikitaguchi.html</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>船橋習志野店</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/funabashinarashino.html</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ピタットハウス</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>横浜西口店</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/shopDetail/yokohamanishiguchi.html</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>632店舗(2026/3末・直営116+NW516)</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>https://www.pitat.com/</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>https://www.starts.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>三軒茶屋店</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/sangenjaya-hc/</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>中野店</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/nakano-hc/</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>川越店</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-kawagoe/</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>リブマックス</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>千葉店</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://www.livemax.net/livemax-store-list/59657/</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>全国(要確認)</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>リブマックス</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>新都心店</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://www.livemax.net/livemax-store-list/59646/</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>全国(要確認)</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>リブマックス</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>日本橋茅場町店</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://www.livemax.net/livemax-store-list/59755/</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>全国(要確認)</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>リブマックス</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>FC浜松町店</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://www.livemax.net/livemax-store-list/hamamatsucho/</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>全国(要確認)</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>https://www.livemax.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>FC店 検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O223"/>
+  <autoFilter ref="A1:O238"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/tools/store-list-scraper/output/stores_search.xlsx
+++ b/tools/store-list-scraper/output/stores_search.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店舗リスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'店舗リスト'!$A$1:$O$247</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O238"/>
+  <dimension ref="A1:O247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12137,8 +12137,449 @@
         </is>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>王子店</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/oji-hc/</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>池袋西口店</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/ikebukuro-hc/</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>赤羽店</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/akabane-hc/</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>高田馬場店</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/takadanobaba-hc/</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>ハウスコム</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>渋谷店</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://www.housecom.jp/shop/shibuya-hc/</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>グループ約232店舗</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>https://www.housecom.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>大橋店</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000952/</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>エイブル</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>南福岡店</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://shop.able.co.jp/000000955/</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>全国 直営+FC(最新要確認)</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>https://www.able.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>アエラスグループ</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>津田沼店</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/shop/aeras-tsudanuma/</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>首都圏 直営67店舗</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>https://www.aeras-group.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ミニミニ</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>西船橋店</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://minimini.jp/shop/10012/nishifunabashi/</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>グループ約1,000店舗(要確認)</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>https://www.minimini.co.jp/recruit/</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>検索由来・店舗URL要HTTP200確認(run.pyで自動検証)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O238"/>
+  <autoFilter ref="A1:O247"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>